--- a/2026/ANATOLE FRANCE/Marzo/ANATOLE-Marzo.xlsx
+++ b/2026/ANATOLE FRANCE/Marzo/ANATOLE-Marzo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3AB825-5D0F-4842-8536-317D5FFA8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E873BC-2EF9-4839-BF45-806201B6CB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="180">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -405,9 +400,6 @@
     <t>Laura</t>
   </si>
   <si>
-    <t>Ana Maria</t>
-  </si>
-  <si>
     <t>German</t>
   </si>
   <si>
@@ -471,12 +463,6 @@
     <t>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</t>
   </si>
   <si>
-    <t>El mes pasado le pusimos pago al 7C lo que era para el 1B</t>
-  </si>
-  <si>
-    <t>El mes pasado el 8B abono $141.650 y no lo pusimos pago - Creo que se lo pusimos al 7B</t>
-  </si>
-  <si>
     <t>VTO 17/04</t>
   </si>
   <si>
@@ -565,6 +551,21 @@
   </si>
   <si>
     <t>Transferencia no identificada 09/03 Gabriel R. Mouriño</t>
+  </si>
+  <si>
+    <t>Dpto:</t>
+  </si>
+  <si>
+    <t>Nombre: ana</t>
+  </si>
+  <si>
+    <t>La transferencia no identificada del mes pasado es del 2A - Este mes debe abonar $218.371,06.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre: </t>
+  </si>
+  <si>
+    <t>Deposito 300.000 a principios de abril</t>
   </si>
 </sst>
 </file>
@@ -782,7 +783,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -851,7 +852,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1254,7 +1261,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1476,117 +1483,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1624,6 +1522,139 @@
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1702,9 +1733,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1742,9 +1773,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1777,26 +1808,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1829,26 +1843,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2023,30 +2020,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="187" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2055,16 +2052,16 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="165" t="s">
+      <c r="B3" s="188" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="189"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2075,12 +2072,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2088,7 +2085,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2099,57 +2096,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="159" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="159"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="159"/>
-      <c r="C9" s="159"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="186" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="167"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="167"/>
-      <c r="B15" s="167"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
-      <c r="B16" s="167"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="186"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="190" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="190"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="190"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="190"/>
+      <c r="B14" s="190"/>
+      <c r="C14" s="190"/>
+      <c r="D14" s="190"/>
+      <c r="E14" s="190"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="190"/>
+      <c r="B15" s="190"/>
+      <c r="C15" s="190"/>
+      <c r="D15" s="190"/>
+      <c r="E15" s="190"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="190"/>
+      <c r="B16" s="190"/>
+      <c r="C16" s="190"/>
+      <c r="D16" s="190"/>
+      <c r="E16" s="190"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2158,7 +2155,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2167,248 +2164,248 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="180" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="181"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="201">
+      <c r="D22" s="164">
         <v>1012046.6</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="70" t="s">
         <v>119</v>
       </c>
       <c r="B23" s="115"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="201">
+      <c r="D23" s="164">
         <v>-250481.55</v>
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="70" t="s">
         <v>120</v>
       </c>
       <c r="B24" s="115"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="201">
+      <c r="D24" s="164">
         <v>0.95</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="202">
+      <c r="D25" s="165">
         <f>SUM(D22:D24)</f>
         <v>761566</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="201"/>
+      <c r="D26" s="164"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="201"/>
+      <c r="D27" s="164"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="201"/>
+      <c r="D28" s="164"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="203"/>
+      <c r="D29" s="166"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="203"/>
+      <c r="D30" s="166"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="204">
+      <c r="D31" s="167">
         <f>SUM(D26:D30)</f>
         <v>0</v>
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="205"/>
+      <c r="D32" s="168"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
         <v>761566</v>
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
-      <c r="D33" s="206"/>
+      <c r="D33" s="169"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="162" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="163"/>
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="182" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="183"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="201">
+      <c r="D34" s="164">
         <v>45000</v>
       </c>
       <c r="E34" s="105" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="162" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="182" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="163"/>
+      <c r="B35" s="183"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="207">
+      <c r="D35" s="170">
         <v>190000</v>
       </c>
       <c r="E35" s="105" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="208"/>
+      <c r="D36" s="171"/>
       <c r="E36" s="106">
         <f>SUM(D34:D35)</f>
         <v>235000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="209"/>
+      <c r="D37" s="172"/>
       <c r="E37" s="107"/>
     </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="160" t="s">
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="180" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="161"/>
+      <c r="B38" s="181"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="210"/>
+      <c r="D38" s="173"/>
       <c r="E38" s="122" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="160" t="s">
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="180" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="161"/>
+      <c r="B39" s="181"/>
       <c r="C39" s="52"/>
-      <c r="D39" s="211"/>
+      <c r="D39" s="174"/>
       <c r="E39" s="108" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="208"/>
+      <c r="D40" s="171"/>
       <c r="E40" s="109">
         <f>SUM(D38:D39)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="110"/>
       <c r="C41" s="110"/>
-      <c r="D41" s="212"/>
+      <c r="D41" s="175"/>
       <c r="E41" s="111"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="213">
+      <c r="D42" s="176">
         <f>1056.22+603327.99</f>
         <v>604384.21</v>
       </c>
       <c r="E42" s="116" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G42" s="89"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>115</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="214">
+      <c r="D43" s="177">
         <v>45037.35</v>
       </c>
       <c r="E43" s="116" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de MARZO</v>
@@ -2417,7 +2414,7 @@
         <v>117</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="214">
+      <c r="D44" s="177">
         <v>85413.96</v>
       </c>
       <c r="E44" s="117" t="str">
@@ -2425,7 +2422,7 @@
         <v>Transf 12/03</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de MARZO</v>
@@ -2434,7 +2431,7 @@
         <v>116</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="214">
+      <c r="D45" s="177">
         <v>5004.1499999999996</v>
       </c>
       <c r="E45" s="118" t="str">
@@ -2442,177 +2439,177 @@
         <v>Transf 12/03</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
       <c r="B46" s="110"/>
       <c r="C46" s="110"/>
-      <c r="D46" s="215"/>
+      <c r="D46" s="178"/>
       <c r="E46" s="109">
         <f>SUM(D42:D45)</f>
         <v>739839.66999999993</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="110"/>
       <c r="C47" s="110"/>
-      <c r="D47" s="212"/>
+      <c r="D47" s="175"/>
       <c r="E47" s="111"/>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="214">
+      <c r="D48" s="177">
         <v>111579.09</v>
       </c>
       <c r="E48" s="116" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="160" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="180" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="161"/>
+      <c r="B49" s="181"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="214">
+      <c r="D49" s="177">
         <v>817259.25</v>
       </c>
       <c r="E49" s="116" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
-      <c r="D50" s="216"/>
+      <c r="D50" s="179"/>
       <c r="E50" s="109">
         <f>SUM(D48:D49)</f>
         <v>928838.34</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="34"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
-      <c r="D51" s="208"/>
+      <c r="D51" s="171"/>
       <c r="E51" s="112"/>
     </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="119" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="115"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="214">
+      <c r="D52" s="177">
         <v>175500</v>
       </c>
       <c r="E52" s="147" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="119" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" s="115"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="177">
+        <v>10812.5</v>
+      </c>
+      <c r="E53" s="147" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="119" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" s="115"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="177">
+        <v>31400</v>
+      </c>
+      <c r="E54" s="147" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="119" t="s">
-        <v>163</v>
-      </c>
-      <c r="B53" s="157"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="214">
-        <v>10812.5</v>
-      </c>
-      <c r="E53" s="147" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="119" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="157"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="214">
-        <v>31400</v>
-      </c>
-      <c r="E54" s="147" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="119" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B55" s="115"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="214">
+      <c r="D55" s="177">
         <v>150000</v>
       </c>
       <c r="E55" s="147" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="119" t="s">
-        <v>166</v>
-      </c>
-      <c r="B56" s="157"/>
+        <v>163</v>
+      </c>
+      <c r="B56" s="115"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="214">
+      <c r="D56" s="177">
         <v>60000</v>
       </c>
       <c r="E56" s="147" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="160" t="s">
-        <v>159</v>
-      </c>
-      <c r="B57" s="161"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="180" t="s">
+        <v>156</v>
+      </c>
+      <c r="B57" s="181"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="214">
+      <c r="D57" s="177">
         <v>85000</v>
       </c>
       <c r="E57" s="147" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B58" s="157"/>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="70" t="s">
+        <v>158</v>
+      </c>
+      <c r="B58" s="115"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="214">
+      <c r="D58" s="177">
         <v>80000</v>
       </c>
       <c r="E58" s="147" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="119" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B59" s="115"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="214">
+      <c r="D59" s="177">
         <v>85000</v>
       </c>
       <c r="E59" s="147" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="29" t="s">
         <v>8</v>
       </c>
@@ -2624,39 +2621,39 @@
         <v>677712.5</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="34" t="s">
         <v>11</v>
       </c>
       <c r="B61" s="59"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="205"/>
+      <c r="D61" s="168"/>
       <c r="E61" s="112"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="214">
+      <c r="D62" s="177">
         <v>57500</v>
       </c>
       <c r="E62" s="114"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="214">
+      <c r="D63" s="177">
         <f>600+69416.74</f>
         <v>70016.740000000005</v>
       </c>
       <c r="E63" s="39"/>
     </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="50" t="s">
         <v>15</v>
       </c>
@@ -2668,14 +2665,14 @@
         <v>127516.74</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="67"/>
       <c r="E65" s="75"/>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="30" t="s">
         <v>46</v>
       </c>
@@ -2684,13 +2681,13 @@
       <c r="D66" s="76"/>
       <c r="E66" s="77"/>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="D67" s="78"/>
       <c r="E67" s="79"/>
       <c r="F67" s="42"/>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>12</v>
       </c>
@@ -2709,7 +2706,7 @@
       <c r="K68" s="89"/>
       <c r="L68" s="89"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D69" s="78"/>
       <c r="E69" s="78"/>
       <c r="H69" s="89"/>
@@ -2718,12 +2715,12 @@
       <c r="K69" s="89"/>
       <c r="L69" s="89"/>
     </row>
-    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D70" s="78"/>
       <c r="E70" s="78"/>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>41</v>
       </c>
@@ -2732,35 +2729,35 @@
       <c r="D71" s="82"/>
       <c r="E71" s="83"/>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="160"/>
-      <c r="B72" s="161"/>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="180"/>
+      <c r="B72" s="181"/>
       <c r="C72" s="5"/>
       <c r="D72" s="93"/>
       <c r="E72" s="69"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="160"/>
-      <c r="B73" s="161"/>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="180"/>
+      <c r="B73" s="181"/>
       <c r="C73" s="5"/>
       <c r="D73" s="71"/>
       <c r="E73" s="69"/>
     </row>
-    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="162"/>
-      <c r="B74" s="163"/>
+    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="182"/>
+      <c r="B74" s="183"/>
       <c r="C74" s="5"/>
       <c r="D74" s="71"/>
       <c r="E74" s="69"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="70"/>
       <c r="B75" s="72"/>
       <c r="C75" s="5"/>
       <c r="D75" s="71"/>
       <c r="E75" s="69"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="48"/>
       <c r="B76" s="47"/>
       <c r="C76" s="47"/>
@@ -2770,9 +2767,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="150" t="s">
         <v>19</v>
       </c>
@@ -2781,8 +2778,8 @@
       <c r="D79" s="152"/>
       <c r="E79" s="153"/>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>20</v>
       </c>
@@ -2794,8 +2791,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="65" t="s">
         <v>13</v>
       </c>
@@ -2804,7 +2801,7 @@
         <v>3470473.25</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="65" t="s">
         <v>14</v>
       </c>
@@ -2813,7 +2810,7 @@
         <v>3470473.25</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="65" t="s">
         <v>21</v>
       </c>
@@ -2822,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="65" t="s">
         <v>37</v>
       </c>
@@ -2831,42 +2828,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="168"/>
-      <c r="B89" s="168"/>
-      <c r="C89" s="168"/>
-      <c r="D89" s="168"/>
-      <c r="E89" s="168"/>
-    </row>
-    <row r="90" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="168"/>
-      <c r="B90" s="168"/>
-      <c r="C90" s="168"/>
-      <c r="D90" s="168"/>
-      <c r="E90" s="168"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="168"/>
-      <c r="B91" s="168"/>
-      <c r="C91" s="168"/>
-      <c r="D91" s="168"/>
-      <c r="E91" s="168"/>
-    </row>
-    <row r="93" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="184"/>
+      <c r="B89" s="184"/>
+      <c r="C89" s="184"/>
+      <c r="D89" s="184"/>
+      <c r="E89" s="184"/>
+    </row>
+    <row r="90" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="184"/>
+      <c r="B90" s="184"/>
+      <c r="C90" s="184"/>
+      <c r="D90" s="184"/>
+      <c r="E90" s="184"/>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="184"/>
+      <c r="B91" s="184"/>
+      <c r="C91" s="184"/>
+      <c r="D91" s="184"/>
+      <c r="E91" s="184"/>
+    </row>
+    <row r="93" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22"/>
       <c r="B93" s="90"/>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="32"/>
       <c r="B94" s="56">
         <v>0</v>
       </c>
       <c r="C94" s="25"/>
     </row>
-    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="s">
         <v>7</v>
       </c>
@@ -2876,14 +2873,14 @@
       </c>
       <c r="C95" s="23"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="24"/>
       <c r="B96" s="39">
         <v>0</v>
       </c>
       <c r="C96" s="23"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="s">
         <v>38</v>
       </c>
@@ -2893,19 +2890,19 @@
       </c>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="27"/>
       <c r="B98" s="46"/>
       <c r="C98" s="23"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="88" t="s">
         <v>42</v>
       </c>
       <c r="B99" s="46"/>
       <c r="C99" s="23"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="38" t="s">
         <v>22</v>
       </c>
@@ -2915,7 +2912,7 @@
       </c>
       <c r="C100" s="23"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="27" t="s">
         <v>23</v>
       </c>
@@ -2925,7 +2922,7 @@
       </c>
       <c r="C101" s="23"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="31" t="s">
         <v>8</v>
       </c>
@@ -2936,25 +2933,25 @@
       <c r="C102" s="26"/>
       <c r="D102" s="42"/>
     </row>
-    <row r="103" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="40"/>
       <c r="C103" s="26"/>
       <c r="D103" s="42"/>
       <c r="E103" s="91"/>
       <c r="F103" s="92"/>
     </row>
-    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41"/>
       <c r="C104" s="26"/>
     </row>
-    <row r="105" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105"/>
       <c r="B105" s="40"/>
       <c r="C105" s="36"/>
     </row>
-    <row r="106" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B106" s="149">
         <v>4494193.4000000004</v>
@@ -2962,16 +2959,16 @@
       <c r="C106" s="36"/>
       <c r="D106" s="45"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B107" s="199">
+      <c r="B107" s="162">
         <f>-B84</f>
         <v>-3470473.25</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="52" t="s">
         <v>48</v>
       </c>
@@ -2980,23 +2977,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="B109" s="199">
+        <v>171</v>
+      </c>
+      <c r="B109" s="162">
         <v>-141652</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="B110" s="199">
+        <v>173</v>
+      </c>
+      <c r="B110" s="162">
         <v>-300000</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="52" t="s">
         <v>122</v>
       </c>
@@ -3004,7 +3001,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="52" t="s">
         <v>51</v>
       </c>
@@ -3013,7 +3010,7 @@
         <v>231879</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="52" t="s">
         <v>49</v>
       </c>
@@ -3022,7 +3019,7 @@
         <v>4405361.22</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="97" t="s">
         <v>44</v>
       </c>
@@ -3033,26 +3030,26 @@
       <c r="D114" s="42"/>
       <c r="E114" s="42"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="96"/>
       <c r="B115" s="96"/>
     </row>
-    <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="169" t="s">
+    <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="185" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="169"/>
-      <c r="C117" s="169"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="169"/>
-      <c r="B118" s="169"/>
-      <c r="C118" s="169"/>
-    </row>
-    <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="185"/>
+      <c r="C117" s="185"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="185"/>
+      <c r="B118" s="185"/>
+      <c r="C118" s="185"/>
+    </row>
+    <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="85" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B119" s="35">
         <v>231879</v>
@@ -3062,13 +3059,13 @@
       </c>
       <c r="E119" s="101"/>
     </row>
-    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="85"/>
       <c r="B120" s="87"/>
       <c r="C120" s="84"/>
       <c r="D120" s="101"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="43" t="s">
         <v>8</v>
       </c>
@@ -3078,44 +3075,44 @@
       </c>
       <c r="C121" s="44"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M122" s="7"/>
     </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="168"/>
-      <c r="B123" s="168"/>
-      <c r="C123" s="168"/>
-      <c r="D123" s="168"/>
-      <c r="E123" s="168"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="168"/>
-      <c r="B124" s="168"/>
-      <c r="C124" s="168"/>
-      <c r="D124" s="168"/>
-      <c r="E124" s="168"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="168"/>
-      <c r="B125" s="168"/>
-      <c r="C125" s="168"/>
-      <c r="D125" s="168"/>
-      <c r="E125" s="168"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="168"/>
-      <c r="B126" s="168"/>
-      <c r="C126" s="168"/>
-      <c r="D126" s="168"/>
-      <c r="E126" s="168"/>
+    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="184"/>
+      <c r="B123" s="184"/>
+      <c r="C123" s="184"/>
+      <c r="D123" s="184"/>
+      <c r="E123" s="184"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="184"/>
+      <c r="B124" s="184"/>
+      <c r="C124" s="184"/>
+      <c r="D124" s="184"/>
+      <c r="E124" s="184"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="184"/>
+      <c r="B125" s="184"/>
+      <c r="C125" s="184"/>
+      <c r="D125" s="184"/>
+      <c r="E125" s="184"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="184"/>
+      <c r="B126" s="184"/>
+      <c r="C126" s="184"/>
+      <c r="D126" s="184"/>
+      <c r="E126" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A123:E126"/>
     <mergeCell ref="A117:C118"/>
@@ -3123,11 +3120,11 @@
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3138,42 +3135,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3197,7 +3194,7 @@
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3212,113 +3209,113 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="184" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="186"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="187"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="188"/>
-      <c r="M5" s="189"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="190"/>
-      <c r="B6" s="191"/>
-      <c r="C6" s="191"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="191"/>
-      <c r="I6" s="191"/>
-      <c r="J6" s="191"/>
-      <c r="K6" s="191"/>
-      <c r="L6" s="191"/>
-      <c r="M6" s="192"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="171" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="200" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="201"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="201"/>
+      <c r="K4" s="201"/>
+      <c r="L4" s="201"/>
+      <c r="M4" s="202"/>
+    </row>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="203"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="204"/>
+    </row>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="205"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="207"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="195" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="171" t="s">
+      <c r="B7" s="195" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="171" t="s">
+      <c r="E7" s="195" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="181" t="s">
+      <c r="F7" s="193" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="171" t="s">
+      <c r="G7" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="182" t="s">
+      <c r="H7" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="181" t="s">
+      <c r="I7" s="193" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="181" t="s">
+      <c r="J7" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="183" t="s">
+      <c r="K7" s="198" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="158" t="s">
+      <c r="L7" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="191" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="171"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="170"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="179"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="178"/>
-      <c r="K8" s="180"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="195"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="197"/>
+      <c r="I8" s="194"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="199"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="M8" s="176"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="191"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="123">
         <v>1</v>
       </c>
@@ -3329,7 +3326,7 @@
         <v>87</v>
       </c>
       <c r="D9" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" s="145">
         <v>3.43</v>
@@ -3369,7 +3366,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="132">
         <f>A9+1</f>
         <v>2</v>
@@ -3422,7 +3419,7 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="132">
         <f t="shared" ref="A11:A32" si="6">A10+1</f>
         <v>3</v>
@@ -3434,7 +3431,7 @@
         <v>89</v>
       </c>
       <c r="D11" s="133" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E11" s="146">
         <f>5.78+1.02</f>
@@ -3476,10 +3473,10 @@
         <v>0.03</v>
       </c>
       <c r="O11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="123">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3491,7 +3488,7 @@
         <v>90</v>
       </c>
       <c r="D12" s="131" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="145">
         <v>3.43</v>
@@ -3532,7 +3529,7 @@
       </c>
       <c r="P12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="123">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3584,29 +3581,25 @@
       </c>
       <c r="P13" s="42"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="123">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="228">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="B14" s="123" t="s">
+      <c r="B14" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="123" t="s">
+      <c r="C14" s="228" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="123" t="s">
-        <v>124</v>
-      </c>
+      <c r="D14" s="228"/>
       <c r="E14" s="145">
         <v>5.69</v>
       </c>
       <c r="F14" s="125">
         <v>225125.06</v>
       </c>
-      <c r="G14" s="134">
-        <v>0</v>
-      </c>
+      <c r="G14" s="134"/>
       <c r="H14" s="126">
         <f t="shared" si="0"/>
         <v>225125.06</v>
@@ -3636,7 +3629,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="123">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3687,7 +3680,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="123">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3699,7 +3692,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="131" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E16" s="145">
         <v>2.95</v>
@@ -3737,7 +3730,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="123">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3746,10 +3739,10 @@
         <v>76</v>
       </c>
       <c r="C17" s="123" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D17" s="131" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="145">
         <v>5.69</v>
@@ -3790,7 +3783,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="123">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3802,7 +3795,7 @@
         <v>95</v>
       </c>
       <c r="D18" s="131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E18" s="145">
         <v>3.43</v>
@@ -3842,7 +3835,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="123">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3851,10 +3844,10 @@
         <v>77</v>
       </c>
       <c r="C19" s="123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" s="131" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E19" s="145">
         <v>2.95</v>
@@ -3894,7 +3887,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="123">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3903,10 +3896,10 @@
         <v>78</v>
       </c>
       <c r="C20" s="123" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D20" s="131" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E20" s="145">
         <f>5.69+0.51</f>
@@ -3947,7 +3940,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="123">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3959,7 +3952,7 @@
         <v>96</v>
       </c>
       <c r="D21" s="131" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E21" s="145">
         <v>3.43</v>
@@ -4000,7 +3993,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="123">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -4012,7 +4005,7 @@
         <v>97</v>
       </c>
       <c r="D22" s="131" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E22" s="145">
         <v>2.95</v>
@@ -4053,7 +4046,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="132">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -4065,7 +4058,7 @@
         <v>98</v>
       </c>
       <c r="D23" s="133" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23" s="146">
         <f>5.69+0.51</f>
@@ -4107,7 +4100,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="123">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -4157,7 +4150,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="123">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -4169,7 +4162,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="131" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E25" s="145">
         <v>2.95</v>
@@ -4210,7 +4203,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="132">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -4221,7 +4214,7 @@
       <c r="C26" s="132" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="193"/>
+      <c r="D26" s="156"/>
       <c r="E26" s="146">
         <f>5.69+0.51</f>
         <v>6.2</v>
@@ -4261,7 +4254,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="132">
         <f t="shared" si="6"/>
         <v>19</v>
@@ -4270,10 +4263,10 @@
         <v>69</v>
       </c>
       <c r="C27" s="132" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D27" s="133" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E27" s="146">
         <v>3.43</v>
@@ -4282,7 +4275,7 @@
         <f>149147.19+141652</f>
         <v>290799.19</v>
       </c>
-      <c r="G27" s="200">
+      <c r="G27" s="163">
         <v>116717.02</v>
       </c>
       <c r="H27" s="126">
@@ -4314,19 +4307,19 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="132">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B28" s="194" t="s">
+      <c r="B28" s="157" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="133" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E28" s="146">
         <v>2.95</v>
@@ -4366,19 +4359,19 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="132">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B29" s="194" t="s">
+      <c r="B29" s="157" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="195" t="s">
+      <c r="C29" s="158" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="133" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E29" s="146">
         <f>5.69+0.51</f>
@@ -4420,19 +4413,19 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="132">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="229">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="230" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="132" t="s">
+      <c r="C30" s="229" t="s">
         <v>103</v>
       </c>
       <c r="D30" s="133" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30" s="146">
         <v>3.43</v>
@@ -4472,19 +4465,19 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="132">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="159" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="197" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="198" t="s">
-        <v>171</v>
+      <c r="C31" s="160" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="161" t="s">
+        <v>168</v>
       </c>
       <c r="E31" s="146">
         <v>2.95</v>
@@ -4524,7 +4517,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="123">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -4575,11 +4568,11 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="172" t="s">
+    <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="209" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="173"/>
+      <c r="B33" s="210"/>
       <c r="C33" s="138" t="s">
         <v>105</v>
       </c>
@@ -4620,15 +4613,15 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="O33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="174" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="211" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="174"/>
-      <c r="C34" s="175"/>
+      <c r="B34" s="211"/>
+      <c r="C34" s="212"/>
       <c r="D34" s="140"/>
       <c r="E34" s="148">
         <f>SUM(E9:E33)</f>
@@ -4667,88 +4660,96 @@
         <v>5260385.2500000009</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="168" t="str">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="184" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
-    </row>
-    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="168"/>
-      <c r="D38" s="168"/>
-      <c r="E38" s="168"/>
-      <c r="F38" s="168"/>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
-      <c r="I38" s="168"/>
-      <c r="J38" s="168"/>
-      <c r="K38" s="168"/>
-      <c r="L38" s="168"/>
-    </row>
-    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="168"/>
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="168"/>
-      <c r="K39" s="168"/>
-      <c r="L39" s="168"/>
-    </row>
-    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="168"/>
-      <c r="D40" s="168"/>
-      <c r="E40" s="168"/>
-      <c r="F40" s="168"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
-      <c r="I40" s="168"/>
-      <c r="J40" s="168"/>
-      <c r="K40" s="168"/>
-      <c r="L40" s="168"/>
-    </row>
-    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="168"/>
-      <c r="D41" s="168"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="168"/>
-      <c r="I41" s="168"/>
-      <c r="J41" s="168"/>
-      <c r="K41" s="168"/>
-      <c r="L41" s="168"/>
-    </row>
-    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="168"/>
-      <c r="D42" s="168"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="168"/>
-      <c r="H42" s="168"/>
-      <c r="I42" s="168"/>
-      <c r="J42" s="168"/>
-      <c r="K42" s="168"/>
-      <c r="L42" s="168"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+    </row>
+    <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="184"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="184"/>
+      <c r="G38" s="184"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="184"/>
+      <c r="J38" s="184"/>
+      <c r="K38" s="184"/>
+      <c r="L38" s="184"/>
+    </row>
+    <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="184"/>
+      <c r="D39" s="184"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="184"/>
+      <c r="G39" s="184"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="184"/>
+      <c r="J39" s="184"/>
+      <c r="K39" s="184"/>
+      <c r="L39" s="184"/>
+    </row>
+    <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="184"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="184"/>
+    </row>
+    <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="184"/>
+      <c r="D41" s="184"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="184"/>
+      <c r="G41" s="184"/>
+      <c r="H41" s="184"/>
+      <c r="I41" s="184"/>
+      <c r="J41" s="184"/>
+      <c r="K41" s="184"/>
+      <c r="L41" s="184"/>
+    </row>
+    <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="184"/>
+      <c r="D42" s="184"/>
+      <c r="E42" s="184"/>
+      <c r="F42" s="184"/>
+      <c r="G42" s="184"/>
+      <c r="H42" s="184"/>
+      <c r="I42" s="184"/>
+      <c r="J42" s="184"/>
+      <c r="K42" s="184"/>
+      <c r="L42" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4758,14 +4759,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4774,20 +4767,146 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="B4:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:G19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="155" t="s">
-        <v>147</v>
-      </c>
+    <row r="3" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="218" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="219" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="214"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="220" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="221"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="216"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="217"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="215"/>
+      <c r="G6" s="216"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="222" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="224"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="222"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="224"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="222"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="224"/>
+    </row>
+    <row r="10" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="225"/>
+      <c r="C10" s="226"/>
+      <c r="D10" s="226"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="227"/>
+    </row>
+    <row r="12" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="231" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="232" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="213"/>
+      <c r="E13" s="213"/>
+      <c r="F13" s="213"/>
+      <c r="G13" s="214"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="233" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="234" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="215"/>
+      <c r="G14" s="216"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="217"/>
+      <c r="C15" s="215"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="215"/>
+      <c r="G15" s="216"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="222" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="224"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="222"/>
+      <c r="C17" s="223"/>
+      <c r="D17" s="223"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="224"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="222"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="224"/>
+    </row>
+    <row r="19" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="225"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="227"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B7:G10"/>
+    <mergeCell ref="B16:G19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/ANATOLE FRANCE/Marzo/ANATOLE-Marzo.xlsx
+++ b/2026/ANATOLE FRANCE/Marzo/ANATOLE-Marzo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3AB825-5D0F-4842-8536-317D5FFA8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2D4CAA-6731-43FE-BACD-E07ED2BC7999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="179">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -565,6 +565,9 @@
   </si>
   <si>
     <t>Transferencia no identificada 09/03 Gabriel R. Mouriño</t>
+  </si>
+  <si>
+    <t>141652+116717,02</t>
   </si>
 </sst>
 </file>
@@ -1486,108 +1489,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1623,6 +1524,108 @@
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2039,11 +2042,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="190" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
       <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2057,12 +2060,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="165" t="s">
+      <c r="B3" s="191" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="166"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="192"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -2100,49 +2103,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="159" t="s">
+      <c r="B8" s="189" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="159"/>
+      <c r="C8" s="189"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="159"/>
-      <c r="C9" s="159"/>
+      <c r="B9" s="189"/>
+      <c r="C9" s="189"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
+      <c r="B10" s="189"/>
+      <c r="C10" s="189"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167" t="s">
+      <c r="A13" s="193" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="167"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167"/>
-      <c r="B14" s="167"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="167"/>
+      <c r="A14" s="193"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+      <c r="E14" s="193"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="167"/>
-      <c r="B15" s="167"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
     </row>
     <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167"/>
-      <c r="B16" s="167"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2168,12 +2171,12 @@
       <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160" t="s">
+      <c r="A22" s="183" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="161"/>
+      <c r="B22" s="184"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="201">
+      <c r="D22" s="167">
         <v>1012046.6</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -2186,7 +2189,7 @@
       </c>
       <c r="B23" s="115"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="201">
+      <c r="D23" s="167">
         <v>-250481.55</v>
       </c>
       <c r="E23" s="5"/>
@@ -2197,7 +2200,7 @@
       </c>
       <c r="B24" s="115"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="201">
+      <c r="D24" s="167">
         <v>0.95</v>
       </c>
       <c r="E24" s="5"/>
@@ -2208,7 +2211,7 @@
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
-      <c r="D25" s="202">
+      <c r="D25" s="168">
         <f>SUM(D22:D24)</f>
         <v>761566</v>
       </c>
@@ -2221,28 +2224,28 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="201"/>
+      <c r="D26" s="167"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="201"/>
+      <c r="D27" s="167"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="201"/>
+      <c r="D28" s="167"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="203"/>
+      <c r="D29" s="169"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2251,7 +2254,7 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="203"/>
+      <c r="D30" s="169"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2260,7 +2263,7 @@
       </c>
       <c r="B31" s="54"/>
       <c r="C31" s="54"/>
-      <c r="D31" s="204">
+      <c r="D31" s="170">
         <f>SUM(D26:D30)</f>
         <v>0</v>
       </c>
@@ -2272,7 +2275,7 @@
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
-      <c r="D32" s="205"/>
+      <c r="D32" s="171"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
         <v>761566</v>
@@ -2285,16 +2288,16 @@
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
-      <c r="D33" s="206"/>
+      <c r="D33" s="172"/>
       <c r="E33" s="104"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="162" t="s">
+      <c r="A34" s="185" t="s">
         <v>152</v>
       </c>
-      <c r="B34" s="163"/>
+      <c r="B34" s="186"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="201">
+      <c r="D34" s="167">
         <v>45000</v>
       </c>
       <c r="E34" s="105" t="s">
@@ -2302,12 +2305,12 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="162" t="s">
+      <c r="A35" s="185" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="163"/>
+      <c r="B35" s="186"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="207">
+      <c r="D35" s="173">
         <v>190000</v>
       </c>
       <c r="E35" s="105" t="s">
@@ -2320,7 +2323,7 @@
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="208"/>
+      <c r="D36" s="174"/>
       <c r="E36" s="106">
         <f>SUM(D34:D35)</f>
         <v>235000</v>
@@ -2332,27 +2335,27 @@
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="209"/>
+      <c r="D37" s="175"/>
       <c r="E37" s="107"/>
     </row>
     <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="160" t="s">
+      <c r="A38" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="161"/>
+      <c r="B38" s="184"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="210"/>
+      <c r="D38" s="176"/>
       <c r="E38" s="122" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="160" t="s">
+      <c r="A39" s="183" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="161"/>
+      <c r="B39" s="184"/>
       <c r="C39" s="52"/>
-      <c r="D39" s="211"/>
+      <c r="D39" s="177"/>
       <c r="E39" s="108" t="s">
         <v>111</v>
       </c>
@@ -2363,7 +2366,7 @@
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="208"/>
+      <c r="D40" s="174"/>
       <c r="E40" s="109">
         <f>SUM(D38:D39)</f>
         <v>0</v>
@@ -2375,7 +2378,7 @@
       </c>
       <c r="B41" s="110"/>
       <c r="C41" s="110"/>
-      <c r="D41" s="212"/>
+      <c r="D41" s="178"/>
       <c r="E41" s="111"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2384,7 +2387,7 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="213">
+      <c r="D42" s="179">
         <f>1056.22+603327.99</f>
         <v>604384.21</v>
       </c>
@@ -2401,7 +2404,7 @@
         <v>115</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="214">
+      <c r="D43" s="180">
         <v>45037.35</v>
       </c>
       <c r="E43" s="116" t="s">
@@ -2417,7 +2420,7 @@
         <v>117</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="214">
+      <c r="D44" s="180">
         <v>85413.96</v>
       </c>
       <c r="E44" s="117" t="str">
@@ -2434,7 +2437,7 @@
         <v>116</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="214">
+      <c r="D45" s="180">
         <v>5004.1499999999996</v>
       </c>
       <c r="E45" s="118" t="str">
@@ -2448,7 +2451,7 @@
       </c>
       <c r="B46" s="110"/>
       <c r="C46" s="110"/>
-      <c r="D46" s="215"/>
+      <c r="D46" s="181"/>
       <c r="E46" s="109">
         <f>SUM(D42:D45)</f>
         <v>739839.66999999993</v>
@@ -2460,7 +2463,7 @@
       </c>
       <c r="B47" s="110"/>
       <c r="C47" s="110"/>
-      <c r="D47" s="212"/>
+      <c r="D47" s="178"/>
       <c r="E47" s="111"/>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2469,7 +2472,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="214">
+      <c r="D48" s="180">
         <v>111579.09</v>
       </c>
       <c r="E48" s="116" t="s">
@@ -2477,12 +2480,12 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="160" t="s">
+      <c r="A49" s="183" t="s">
         <v>113</v>
       </c>
-      <c r="B49" s="161"/>
+      <c r="B49" s="184"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="214">
+      <c r="D49" s="180">
         <v>817259.25</v>
       </c>
       <c r="E49" s="116" t="s">
@@ -2495,7 +2498,7 @@
       </c>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
-      <c r="D50" s="216"/>
+      <c r="D50" s="182"/>
       <c r="E50" s="109">
         <f>SUM(D48:D49)</f>
         <v>928838.34</v>
@@ -2505,7 +2508,7 @@
       <c r="A51" s="34"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
-      <c r="D51" s="208"/>
+      <c r="D51" s="174"/>
       <c r="E51" s="112"/>
     </row>
     <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2514,7 +2517,7 @@
       </c>
       <c r="B52" s="115"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="214">
+      <c r="D52" s="180">
         <v>175500</v>
       </c>
       <c r="E52" s="147" t="s">
@@ -2527,7 +2530,7 @@
       </c>
       <c r="B53" s="157"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="214">
+      <c r="D53" s="180">
         <v>10812.5</v>
       </c>
       <c r="E53" s="147" t="s">
@@ -2540,7 +2543,7 @@
       </c>
       <c r="B54" s="157"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="214">
+      <c r="D54" s="180">
         <v>31400</v>
       </c>
       <c r="E54" s="147" t="s">
@@ -2553,7 +2556,7 @@
       </c>
       <c r="B55" s="115"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="214">
+      <c r="D55" s="180">
         <v>150000</v>
       </c>
       <c r="E55" s="147" t="s">
@@ -2566,7 +2569,7 @@
       </c>
       <c r="B56" s="157"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="214">
+      <c r="D56" s="180">
         <v>60000</v>
       </c>
       <c r="E56" s="147" t="s">
@@ -2574,12 +2577,12 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="160" t="s">
+      <c r="A57" s="183" t="s">
         <v>159</v>
       </c>
-      <c r="B57" s="161"/>
+      <c r="B57" s="184"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="214">
+      <c r="D57" s="180">
         <v>85000</v>
       </c>
       <c r="E57" s="147" t="s">
@@ -2592,7 +2595,7 @@
       </c>
       <c r="B58" s="157"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="214">
+      <c r="D58" s="180">
         <v>80000</v>
       </c>
       <c r="E58" s="147" t="s">
@@ -2605,7 +2608,7 @@
       </c>
       <c r="B59" s="115"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="214">
+      <c r="D59" s="180">
         <v>85000</v>
       </c>
       <c r="E59" s="147" t="s">
@@ -2630,7 +2633,7 @@
       </c>
       <c r="B61" s="59"/>
       <c r="C61" s="29"/>
-      <c r="D61" s="205"/>
+      <c r="D61" s="171"/>
       <c r="E61" s="112"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2639,7 +2642,7 @@
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="214">
+      <c r="D62" s="180">
         <v>57500</v>
       </c>
       <c r="E62" s="114"/>
@@ -2650,7 +2653,7 @@
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="214">
+      <c r="D63" s="180">
         <f>600+69416.74</f>
         <v>70016.740000000005</v>
       </c>
@@ -2733,22 +2736,22 @@
       <c r="E71" s="83"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="160"/>
-      <c r="B72" s="161"/>
+      <c r="A72" s="183"/>
+      <c r="B72" s="184"/>
       <c r="C72" s="5"/>
       <c r="D72" s="93"/>
       <c r="E72" s="69"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="160"/>
-      <c r="B73" s="161"/>
+      <c r="A73" s="183"/>
+      <c r="B73" s="184"/>
       <c r="C73" s="5"/>
       <c r="D73" s="71"/>
       <c r="E73" s="69"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="162"/>
-      <c r="B74" s="163"/>
+      <c r="A74" s="185"/>
+      <c r="B74" s="186"/>
       <c r="C74" s="5"/>
       <c r="D74" s="71"/>
       <c r="E74" s="69"/>
@@ -2834,25 +2837,25 @@
     <row r="87" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="88" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="168"/>
-      <c r="B89" s="168"/>
-      <c r="C89" s="168"/>
-      <c r="D89" s="168"/>
-      <c r="E89" s="168"/>
+      <c r="A89" s="187"/>
+      <c r="B89" s="187"/>
+      <c r="C89" s="187"/>
+      <c r="D89" s="187"/>
+      <c r="E89" s="187"/>
     </row>
     <row r="90" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="168"/>
-      <c r="B90" s="168"/>
-      <c r="C90" s="168"/>
-      <c r="D90" s="168"/>
-      <c r="E90" s="168"/>
+      <c r="A90" s="187"/>
+      <c r="B90" s="187"/>
+      <c r="C90" s="187"/>
+      <c r="D90" s="187"/>
+      <c r="E90" s="187"/>
     </row>
     <row r="91" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="168"/>
-      <c r="B91" s="168"/>
-      <c r="C91" s="168"/>
-      <c r="D91" s="168"/>
-      <c r="E91" s="168"/>
+      <c r="A91" s="187"/>
+      <c r="B91" s="187"/>
+      <c r="C91" s="187"/>
+      <c r="D91" s="187"/>
+      <c r="E91" s="187"/>
     </row>
     <row r="93" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22"/>
@@ -2872,7 +2875,7 @@
       </c>
       <c r="B95" s="39">
         <f>PRORRATEO!G34</f>
-        <v>4405361.22</v>
+        <v>4263709.22</v>
       </c>
       <c r="C95" s="23"/>
     </row>
@@ -2931,7 +2934,7 @@
       </c>
       <c r="B102" s="56">
         <f>SUM(B94:B101)</f>
-        <v>1166766.9699999997</v>
+        <v>1025114.9699999997</v>
       </c>
       <c r="C102" s="26"/>
       <c r="D102" s="42"/>
@@ -2966,7 +2969,7 @@
       <c r="A107" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B107" s="199">
+      <c r="B107" s="165">
         <f>-B84</f>
         <v>-3470473.25</v>
       </c>
@@ -2984,7 +2987,7 @@
       <c r="A109" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="B109" s="199">
+      <c r="B109" s="165">
         <v>-141652</v>
       </c>
     </row>
@@ -2992,7 +2995,7 @@
       <c r="A110" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="B110" s="199">
+      <c r="B110" s="165">
         <v>-300000</v>
       </c>
     </row>
@@ -3019,7 +3022,7 @@
       </c>
       <c r="B113" s="100">
         <f>PRORRATEO!G34</f>
-        <v>4405361.22</v>
+        <v>4263709.22</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3028,7 +3031,7 @@
       </c>
       <c r="B114" s="98">
         <f>SUM(B106:C113)</f>
-        <v>5539308.3700000001</v>
+        <v>5397656.3700000001</v>
       </c>
       <c r="D114" s="42"/>
       <c r="E114" s="42"/>
@@ -3039,16 +3042,16 @@
     </row>
     <row r="116" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="169" t="s">
+      <c r="A117" s="188" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="169"/>
-      <c r="C117" s="169"/>
+      <c r="B117" s="188"/>
+      <c r="C117" s="188"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="169"/>
-      <c r="B118" s="169"/>
-      <c r="C118" s="169"/>
+      <c r="A118" s="188"/>
+      <c r="B118" s="188"/>
+      <c r="C118" s="188"/>
     </row>
     <row r="119" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="85" t="s">
@@ -3082,40 +3085,40 @@
       <c r="M122" s="7"/>
     </row>
     <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="168"/>
-      <c r="B123" s="168"/>
-      <c r="C123" s="168"/>
-      <c r="D123" s="168"/>
-      <c r="E123" s="168"/>
+      <c r="A123" s="187"/>
+      <c r="B123" s="187"/>
+      <c r="C123" s="187"/>
+      <c r="D123" s="187"/>
+      <c r="E123" s="187"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="168"/>
-      <c r="B124" s="168"/>
-      <c r="C124" s="168"/>
-      <c r="D124" s="168"/>
-      <c r="E124" s="168"/>
+      <c r="A124" s="187"/>
+      <c r="B124" s="187"/>
+      <c r="C124" s="187"/>
+      <c r="D124" s="187"/>
+      <c r="E124" s="187"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="168"/>
-      <c r="B125" s="168"/>
-      <c r="C125" s="168"/>
-      <c r="D125" s="168"/>
-      <c r="E125" s="168"/>
+      <c r="A125" s="187"/>
+      <c r="B125" s="187"/>
+      <c r="C125" s="187"/>
+      <c r="D125" s="187"/>
+      <c r="E125" s="187"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="168"/>
-      <c r="B126" s="168"/>
-      <c r="C126" s="168"/>
-      <c r="D126" s="168"/>
-      <c r="E126" s="168"/>
+      <c r="A126" s="187"/>
+      <c r="B126" s="187"/>
+      <c r="C126" s="187"/>
+      <c r="D126" s="187"/>
+      <c r="E126" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A123:E126"/>
     <mergeCell ref="A117:C118"/>
@@ -3123,11 +3126,11 @@
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3163,14 +3166,14 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
       <c r="M1" s="6"/>
     </row>
     <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3213,110 +3216,110 @@
       <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="203" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="186"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
+      <c r="I4" s="204"/>
+      <c r="J4" s="204"/>
+      <c r="K4" s="204"/>
+      <c r="L4" s="204"/>
+      <c r="M4" s="205"/>
     </row>
     <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="187"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="188"/>
-      <c r="M5" s="189"/>
+      <c r="A5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="207"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="207"/>
+      <c r="L5" s="207"/>
+      <c r="M5" s="208"/>
     </row>
     <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="190"/>
-      <c r="B6" s="191"/>
-      <c r="C6" s="191"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="191"/>
-      <c r="I6" s="191"/>
-      <c r="J6" s="191"/>
-      <c r="K6" s="191"/>
-      <c r="L6" s="191"/>
-      <c r="M6" s="192"/>
+      <c r="A6" s="209"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="210"/>
+      <c r="K6" s="210"/>
+      <c r="L6" s="210"/>
+      <c r="M6" s="211"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="171" t="s">
+      <c r="B7" s="198" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="171" t="s">
+      <c r="C7" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="171" t="s">
+      <c r="D7" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="171" t="s">
+      <c r="E7" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="181" t="s">
+      <c r="F7" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="171" t="s">
+      <c r="G7" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="182" t="s">
+      <c r="H7" s="199" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="181" t="s">
+      <c r="I7" s="196" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="181" t="s">
+      <c r="J7" s="196" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="183" t="s">
+      <c r="K7" s="201" t="s">
         <v>60</v>
       </c>
       <c r="L7" s="158" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="176" t="s">
+      <c r="M7" s="194" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="171"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="171"/>
-      <c r="D8" s="170"/>
-      <c r="E8" s="171"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="171"/>
-      <c r="H8" s="179"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="178"/>
-      <c r="K8" s="180"/>
+      <c r="A8" s="198"/>
+      <c r="B8" s="212"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="212"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="197"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="200"/>
+      <c r="I8" s="197"/>
+      <c r="J8" s="197"/>
+      <c r="K8" s="202"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/04</v>
       </c>
-      <c r="M8" s="176"/>
+      <c r="M8" s="194"/>
     </row>
     <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="123">
@@ -3389,16 +3392,16 @@
       <c r="F10" s="134">
         <v>262617.02</v>
       </c>
-      <c r="G10" s="134">
-        <v>141652</v>
-      </c>
-      <c r="H10" s="126">
+      <c r="G10" s="134" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="126" t="e">
         <f t="shared" si="0"/>
-        <v>120965.02000000002</v>
-      </c>
-      <c r="I10" s="126">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I10" s="126" t="e">
         <f t="shared" ref="I10:I33" si="3">IF(H10&gt;0,H10*3%,0)</f>
-        <v>3628.9506000000006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J10" s="127">
         <f t="shared" ref="J10:J32" si="4">K$2*E10%</f>
@@ -3408,13 +3411,13 @@
         <f t="shared" ref="K10:K32" si="5">G$2*E10/100</f>
         <v>23644.25</v>
       </c>
-      <c r="L10" s="129">
+      <c r="L10" s="129" t="e">
         <f t="shared" si="1"/>
-        <v>241311.02</v>
-      </c>
-      <c r="M10" s="130">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M10" s="130" t="e">
         <f t="shared" si="2"/>
-        <v>248550.02</v>
+        <v>#VALUE!</v>
       </c>
       <c r="N10" s="42">
         <f>N9+0.01</f>
@@ -4221,7 +4224,7 @@
       <c r="C26" s="132" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="193"/>
+      <c r="D26" s="159"/>
       <c r="E26" s="146">
         <f>5.69+0.51</f>
         <v>6.2</v>
@@ -4282,7 +4285,7 @@
         <f>149147.19+141652</f>
         <v>290799.19</v>
       </c>
-      <c r="G27" s="200">
+      <c r="G27" s="166">
         <v>116717.02</v>
       </c>
       <c r="H27" s="126">
@@ -4319,7 +4322,7 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B28" s="194" t="s">
+      <c r="B28" s="160" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="132" t="s">
@@ -4371,10 +4374,10 @@
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B29" s="194" t="s">
+      <c r="B29" s="160" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="195" t="s">
+      <c r="C29" s="161" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="133" t="s">
@@ -4425,7 +4428,7 @@
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="162" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="132" t="s">
@@ -4477,13 +4480,13 @@
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="162" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="197" t="s">
+      <c r="C31" s="163" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="198" t="s">
+      <c r="D31" s="164" t="s">
         <v>171</v>
       </c>
       <c r="E31" s="146">
@@ -4576,10 +4579,10 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="172" t="s">
+      <c r="A33" s="213" t="s">
         <v>106</v>
       </c>
-      <c r="B33" s="173"/>
+      <c r="B33" s="214"/>
       <c r="C33" s="138" t="s">
         <v>105</v>
       </c>
@@ -4624,11 +4627,11 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="174" t="s">
+      <c r="A34" s="215" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="174"/>
-      <c r="C34" s="175"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="216"/>
       <c r="D34" s="140"/>
       <c r="E34" s="148">
         <f>SUM(E9:E33)</f>
@@ -4640,15 +4643,15 @@
       </c>
       <c r="G34" s="142">
         <f t="shared" si="8"/>
-        <v>4405361.22</v>
-      </c>
-      <c r="H34" s="142">
+        <v>4263709.22</v>
+      </c>
+      <c r="H34" s="142" t="e">
         <f t="shared" si="8"/>
-        <v>1014220.23</v>
-      </c>
-      <c r="I34" s="142">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I34" s="142" t="e">
         <f t="shared" si="8"/>
-        <v>31598.546400000003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J34" s="143">
         <f t="shared" si="8"/>
@@ -4658,13 +4661,13 @@
         <f t="shared" si="8"/>
         <v>822739.74999999988</v>
       </c>
-      <c r="L34" s="144">
+      <c r="L34" s="144" t="e">
         <f>SUM(L9:L26)</f>
-        <v>3717208.7100000004</v>
-      </c>
-      <c r="M34" s="144">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M34" s="144" t="e">
         <f>SUM(M9:M33)</f>
-        <v>5260385.2500000009</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4673,82 +4676,90 @@
     </row>
     <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="168" t="str">
+      <c r="C37" s="187" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
+      <c r="D37" s="187"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="187"/>
+      <c r="K37" s="187"/>
+      <c r="L37" s="187"/>
     </row>
     <row r="38" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="168"/>
-      <c r="D38" s="168"/>
-      <c r="E38" s="168"/>
-      <c r="F38" s="168"/>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
-      <c r="I38" s="168"/>
-      <c r="J38" s="168"/>
-      <c r="K38" s="168"/>
-      <c r="L38" s="168"/>
+      <c r="C38" s="187"/>
+      <c r="D38" s="187"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="187"/>
+      <c r="H38" s="187"/>
+      <c r="I38" s="187"/>
+      <c r="J38" s="187"/>
+      <c r="K38" s="187"/>
+      <c r="L38" s="187"/>
     </row>
     <row r="39" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="168"/>
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="168"/>
-      <c r="K39" s="168"/>
-      <c r="L39" s="168"/>
+      <c r="C39" s="187"/>
+      <c r="D39" s="187"/>
+      <c r="E39" s="187"/>
+      <c r="F39" s="187"/>
+      <c r="G39" s="187"/>
+      <c r="H39" s="187"/>
+      <c r="I39" s="187"/>
+      <c r="J39" s="187"/>
+      <c r="K39" s="187"/>
+      <c r="L39" s="187"/>
     </row>
     <row r="40" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="168"/>
-      <c r="D40" s="168"/>
-      <c r="E40" s="168"/>
-      <c r="F40" s="168"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
-      <c r="I40" s="168"/>
-      <c r="J40" s="168"/>
-      <c r="K40" s="168"/>
-      <c r="L40" s="168"/>
+      <c r="C40" s="187"/>
+      <c r="D40" s="187"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="187"/>
+      <c r="H40" s="187"/>
+      <c r="I40" s="187"/>
+      <c r="J40" s="187"/>
+      <c r="K40" s="187"/>
+      <c r="L40" s="187"/>
     </row>
     <row r="41" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="168"/>
-      <c r="D41" s="168"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="168"/>
-      <c r="I41" s="168"/>
-      <c r="J41" s="168"/>
-      <c r="K41" s="168"/>
-      <c r="L41" s="168"/>
+      <c r="C41" s="187"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="187"/>
+      <c r="H41" s="187"/>
+      <c r="I41" s="187"/>
+      <c r="J41" s="187"/>
+      <c r="K41" s="187"/>
+      <c r="L41" s="187"/>
     </row>
     <row r="42" spans="1:15" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="168"/>
-      <c r="D42" s="168"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="168"/>
-      <c r="H42" s="168"/>
-      <c r="I42" s="168"/>
-      <c r="J42" s="168"/>
-      <c r="K42" s="168"/>
-      <c r="L42" s="168"/>
+      <c r="C42" s="187"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="187"/>
+      <c r="I42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="187"/>
+      <c r="L42" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4758,14 +4769,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
